--- a/generation_zy/hiwo-物料1-1.xlsx
+++ b/generation_zy/hiwo-物料1-1.xlsx
@@ -1714,7 +1714,7 @@
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>溶剂1,DMF</t>
+          <t>Ic1ccccc1</t>
         </is>
       </c>
       <c r="E2" s="6" t="n">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>N2(CCNCC2)C3=CC=CC=C3</t>
+          <t>试剂1,cesium hydroxide</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>空</t>
+          <t>试剂2,palladium diacetate</t>
         </is>
       </c>
       <c r="E4" s="6" t="n">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>空</t>
+          <t>溶剂1,toluene</t>
         </is>
       </c>
       <c r="E5" s="6" t="n">

--- a/generation_zy/hiwo-物料1-1.xlsx
+++ b/generation_zy/hiwo-物料1-1.xlsx
@@ -1714,7 +1714,7 @@
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>Ic1ccccc1</t>
+          <t>N2(CCNCC2)C3=CC=CC=C3</t>
         </is>
       </c>
       <c r="E2" s="6" t="n">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>试剂1,cesium hydroxide</t>
+          <t>DMF</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>试剂2,palladium diacetate</t>
+          <t>空</t>
         </is>
       </c>
       <c r="E4" s="6" t="n">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>溶剂1,toluene</t>
+          <t>空</t>
         </is>
       </c>
       <c r="E5" s="6" t="n">
